--- a/docs/downloads/05/tbl_comfort_marovoay_tous.xlsx
+++ b/docs/downloads/05/tbl_comfort_marovoay_tous.xlsx
@@ -383,10 +383,10 @@
         </is>
       </c>
       <c r="C2">
-        <v>343</v>
+        <v>708</v>
       </c>
       <c r="D2">
-        <v>100</v>
+        <v>495.1</v>
       </c>
     </row>
     <row r="3">
@@ -396,10 +396,10 @@
         </is>
       </c>
       <c r="C3">
-        <v>305</v>
+        <v>621</v>
       </c>
       <c r="D3">
-        <v>100</v>
+        <v>504.9</v>
       </c>
     </row>
     <row r="4">
@@ -409,10 +409,10 @@
         </is>
       </c>
       <c r="C4">
-        <v>321</v>
+        <v>618</v>
       </c>
       <c r="D4">
-        <v>100</v>
+        <v>451.1</v>
       </c>
     </row>
     <row r="5">
@@ -422,10 +422,10 @@
         </is>
       </c>
       <c r="C5">
-        <v>313</v>
+        <v>617</v>
       </c>
       <c r="D5">
-        <v>100</v>
+        <v>531.9</v>
       </c>
     </row>
     <row r="6">
@@ -435,10 +435,10 @@
         </is>
       </c>
       <c r="C6">
-        <v>1282</v>
+        <v>2564</v>
       </c>
       <c r="D6">
-        <v>100</v>
+        <v>494</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/05/tbl_comfort_marovoay_tous.xlsx
+++ b/docs/downloads/05/tbl_comfort_marovoay_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="C2">
@@ -392,7 +392,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="C3">
@@ -405,7 +405,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="C4">
@@ -418,7 +418,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="C5">
@@ -431,7 +431,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="C6">
